--- a/artfynd/A 58056-2024 artfynd.xlsx
+++ b/artfynd/A 58056-2024 artfynd.xlsx
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
